--- a/बजेट माग estimate/वडा बजेट estimate/सुकपानी स्याले सिंचाई कुलो मर्मत/सुकपानी स्याले सिंचाई कुलो मर्मत.xlsx
+++ b/बजेट माग estimate/वडा बजेट estimate/सुकपानी स्याले सिंचाई कुलो मर्मत/सुकपानी स्याले सिंचाई कुलो मर्मत.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E47B63-4EF1-4636-85C0-2D4453E0D295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDCD1D6E-A9E9-48C4-B69C-581C0C925938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,12 +33,13 @@
     <definedName name="description_5">[1]Abstract!$B$171</definedName>
     <definedName name="description_6" localSheetId="0">#REF!</definedName>
     <definedName name="description_6">#REF!</definedName>
+    <definedName name="description_706">[3]Abstract!$B$265</definedName>
     <definedName name="description_759">[1]Abstract!$B$278</definedName>
     <definedName name="description_781" localSheetId="0">#REF!</definedName>
     <definedName name="description_781">#REF!</definedName>
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
     <definedName name="description_784">[3]Abstract!$B$300</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">estimate!$1:$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -57,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -152,9 +153,6 @@
     <t>Project:-सुकपानी स्याले सिंचाई कुलो मर्मत</t>
   </si>
   <si>
-    <t>Date:2082/09/01</t>
-  </si>
-  <si>
     <t>Earthwork Excavation in Cutting., Roadway Excavation in ordinary rock  by Manual Means ., Roadway Excavation  in ordinary rock as per Drawing and Technical specification, including all lift and lead  as per Drawing and instruction of the Engineer.</t>
   </si>
   <si>
@@ -174,6 +172,18 @@
   </si>
   <si>
     <t>-13% VAT for binding wire</t>
+  </si>
+  <si>
+    <t>Laying and fixing of Geo-Textile all complete as per specification., Providing  and laying of a geotextile filter between pitching and embankment slopes as per Drawing and Technical Specifications.</t>
+  </si>
+  <si>
+    <t>-at back of gabion wall</t>
+  </si>
+  <si>
+    <t>m2</t>
+  </si>
+  <si>
+    <t>Date:2082/09/03</t>
   </si>
 </sst>
 </file>
@@ -432,24 +442,7 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -469,7 +462,24 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -685,6 +695,11 @@
         <row r="40">
           <cell r="B40" t="str">
             <v>Excavation for Structures Foundation, Earth work in excavation of foundation of structures, including  construction of shoring and bracing, removal of stumps and other deleterious matter and backfilling with approved Material as per Drawing and Technical Specifications., Ordinary soil by Mechanical Means, Depth upto 3 m</v>
+          </cell>
+        </row>
+        <row r="265">
+          <cell r="B265" t="str">
+            <v>Laying and fixing of Geo-Textile all complete as per specification., Providing  and laying of a geotextile filter between pitching and embankment slopes as per Drawing and Technical Specifications.</v>
           </cell>
         </row>
         <row r="300">
@@ -1004,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:S32"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="19" customWidth="1"/>
@@ -1023,113 +1038,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
     </row>
     <row r="2" spans="1:16" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
     </row>
     <row r="5" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="41"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="49"/>
     </row>
     <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="36"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="37" t="s">
+      <c r="H6" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="37"/>
-      <c r="J6" s="37"/>
-      <c r="K6" s="37"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
     </row>
     <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="45"/>
+      <c r="H7" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
     </row>
     <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
@@ -1171,7 +1186,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
@@ -1186,10 +1201,10 @@
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" s="33">
         <v>6</v>
@@ -1198,7 +1213,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="33">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G10" s="33">
         <f>PRODUCT(C10:F10)</f>
@@ -1265,7 +1280,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
@@ -1280,7 +1295,7 @@
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" s="17">
         <v>6</v>
@@ -1339,16 +1354,16 @@
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
       <c r="K15" s="17"/>
-      <c r="M15" s="49"/>
-      <c r="N15" s="49"/>
-      <c r="O15" s="49"/>
-      <c r="P15" s="49"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="32"/>
       <c r="C16" s="17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="33">
         <v>1</v>
@@ -1361,18 +1376,18 @@
       </c>
       <c r="G16" s="33">
         <f>PRODUCT(C16:F16)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
       <c r="J16" s="17"/>
       <c r="K16" s="17"/>
-      <c r="M16" s="49"/>
-      <c r="N16" s="49"/>
-      <c r="O16" s="49"/>
-      <c r="P16" s="49"/>
-    </row>
-    <row r="17" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+    </row>
+    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="34" t="s">
         <v>17</v>
@@ -1383,7 +1398,7 @@
       <c r="F17" s="5"/>
       <c r="G17" s="6">
         <f>SUM(G14:G16)</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>18</v>
@@ -1393,11 +1408,11 @@
       </c>
       <c r="J17" s="18">
         <f>G17*I17</f>
-        <v>154118.88</v>
+        <v>147697.26</v>
       </c>
       <c r="K17" s="5"/>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="32" t="s">
         <v>28</v>
@@ -1411,14 +1426,14 @@
       <c r="I18" s="17"/>
       <c r="J18" s="18">
         <f>0.13*G17*(16299.36/6+16299.36/6+16299.36/6+16299.36/6)/4</f>
-        <v>8475.6671999999999</v>
+        <v>8122.5144</v>
       </c>
       <c r="K18" s="17"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="16"/>
       <c r="B19" s="32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
@@ -1429,14 +1444,14 @@
       <c r="I19" s="17"/>
       <c r="J19" s="18">
         <f>0.13*G17*(9055.8/6+9346.05/6+10191/6+10185.84/6)/4</f>
-        <v>5041.2297000000008</v>
+        <v>4831.1784625000009</v>
       </c>
       <c r="K19" s="17"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
@@ -1447,14 +1462,14 @@
       <c r="I20" s="17"/>
       <c r="J20" s="18">
         <f>0.13*G17*(1008.78/6+1145.52/6+1393.2/6+1555.74/6)/4</f>
-        <v>663.4212</v>
+        <v>635.77864999999997</v>
       </c>
       <c r="K20" s="17"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="16"/>
       <c r="B21" s="32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C21" s="17"/>
       <c r="D21" s="17"/>
@@ -1465,13 +1480,13 @@
       <c r="I21" s="17"/>
       <c r="J21" s="18">
         <f>0.13*G17*(434.4/6+468/6+600/6+547.2/6)/4</f>
-        <v>266.44799999999998</v>
+        <v>255.346</v>
       </c>
       <c r="K21" s="17"/>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
-      <c r="B22" s="17"/>
+      <c r="B22" s="32"/>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
@@ -1479,179 +1494,264 @@
       <c r="G22" s="17"/>
       <c r="H22" s="17"/>
       <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
+      <c r="J22" s="18"/>
       <c r="K22" s="17"/>
     </row>
-    <row r="23" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+    <row r="23" spans="1:17" ht="123" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="16">
         <v>3</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="16"/>
+      <c r="B24" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="17">
+        <v>1</v>
+      </c>
+      <c r="D24" s="17">
+        <v>6</v>
+      </c>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17">
+        <v>2</v>
+      </c>
+      <c r="G24" s="33">
+        <f>PRODUCT(C24:F24)</f>
+        <v>12</v>
+      </c>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="17"/>
+    </row>
+    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="6">
+        <f>SUM(G22:G24)</f>
+        <v>12</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I25" s="6">
+        <v>161.58000000000001</v>
+      </c>
+      <c r="J25" s="18">
+        <f>G25*I25</f>
+        <v>1938.96</v>
+      </c>
+      <c r="K25" s="5"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" s="16"/>
+      <c r="B26" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="18">
+        <f>0.13*G25*45360/300</f>
+        <v>235.87200000000001</v>
+      </c>
+      <c r="K26" s="17"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="16"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+    </row>
+    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>4</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C28" s="3">
         <v>1</v>
       </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="7">
-        <f t="shared" ref="G23" si="0">PRODUCT(C23:F23)</f>
+      <c r="D28" s="4"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="7">
+        <f t="shared" ref="G28" si="0">PRODUCT(C28:F28)</f>
         <v>1</v>
       </c>
-      <c r="H23" s="7" t="s">
+      <c r="H28" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I23" s="6">
+      <c r="I28" s="6">
         <v>500</v>
       </c>
-      <c r="J23" s="7">
-        <f>G23*I23</f>
+      <c r="J28" s="7">
+        <f>G28*I28</f>
         <v>500</v>
       </c>
-      <c r="K23" s="5"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="18"/>
-      <c r="K24" s="5"/>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A25" s="21"/>
-      <c r="B25" s="22" t="s">
+      <c r="K28" s="5"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="5"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" s="21"/>
+      <c r="B30" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="23"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="18">
-        <f>SUM(J9:J23)</f>
-        <v>174265.6061</v>
-      </c>
-      <c r="K25" s="25"/>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="M26" s="20"/>
-      <c r="N26" s="20"/>
-      <c r="O26" s="20"/>
-      <c r="P26" s="20"/>
-      <c r="Q26" s="20"/>
-      <c r="R26" s="20"/>
-      <c r="S26" s="20"/>
-    </row>
-    <row r="27" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="26"/>
-      <c r="B27" s="27" t="s">
+      <c r="C30" s="23"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="18">
+        <f>SUM(J9:J28)</f>
+        <v>169416.86951250001</v>
+      </c>
+      <c r="K30" s="25"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20"/>
+    </row>
+    <row r="32" spans="1:17" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="26"/>
+      <c r="B32" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="42">
-        <f>J25</f>
-        <v>174265.6061</v>
-      </c>
-      <c r="D27" s="43"/>
-      <c r="E27" s="9">
+      <c r="C32" s="37">
+        <f>J30</f>
+        <v>169416.86951250001</v>
+      </c>
+      <c r="D32" s="38"/>
+      <c r="E32" s="9">
         <v>100</v>
       </c>
-      <c r="F27" s="26"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="29"/>
-      <c r="J27" s="30"/>
-      <c r="K27" s="31"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="19"/>
-      <c r="O27" s="19"/>
-      <c r="P27" s="19"/>
-      <c r="Q27" s="19"/>
-      <c r="R27" s="19"/>
-      <c r="S27" s="19"/>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B28" s="27" t="s">
+      <c r="F32" s="26"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="31"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
+      <c r="Q32" s="19"/>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B33" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="46">
+      <c r="C33" s="41">
         <v>150000</v>
       </c>
-      <c r="D28" s="47"/>
-      <c r="E28" s="9"/>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B29" s="27" t="s">
+      <c r="D33" s="42"/>
+      <c r="E33" s="9"/>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B34" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="46">
-        <f>C28-C31-C32</f>
+      <c r="C34" s="41">
+        <f>C33-C36-C37</f>
         <v>142500</v>
       </c>
-      <c r="D29" s="47"/>
-      <c r="E29" s="9">
-        <f>C29/C27*100</f>
-        <v>81.771729481850969</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B30" s="27" t="s">
+      <c r="D34" s="42"/>
+      <c r="E34" s="9">
+        <f>C34/C32*100</f>
+        <v>84.112048823736515</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B35" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="48">
-        <f>C27-C29</f>
-        <v>31765.606100000005</v>
-      </c>
-      <c r="D30" s="48"/>
-      <c r="E30" s="9">
-        <f>100-E29</f>
-        <v>18.228270518149031</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B31" s="27" t="s">
+      <c r="C35" s="43">
+        <f>C32-C34</f>
+        <v>26916.869512500009</v>
+      </c>
+      <c r="D35" s="43"/>
+      <c r="E35" s="9">
+        <f>100-E34</f>
+        <v>15.887951176263485</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B36" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="42">
-        <f>C28*0.03</f>
+      <c r="C36" s="37">
+        <f>C33*0.03</f>
         <v>4500</v>
       </c>
-      <c r="D31" s="43"/>
-      <c r="E31" s="9">
+      <c r="D36" s="38"/>
+      <c r="E36" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B32" s="27" t="s">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B37" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="42">
-        <f>C28*0.02</f>
+      <c r="C37" s="37">
+        <f>C33*0.02</f>
         <v>3000</v>
       </c>
-      <c r="D32" s="43"/>
-      <c r="E32" s="9">
+      <c r="D37" s="38"/>
+      <c r="E37" s="9">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
     <mergeCell ref="A1:K1"/>
@@ -1659,6 +1759,14 @@
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A5:K5"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>

--- a/बजेट माग estimate/वडा बजेट estimate/सुकपानी स्याले सिंचाई कुलो मर्मत/सुकपानी स्याले सिंचाई कुलो मर्मत.xlsx
+++ b/बजेट माग estimate/वडा बजेट estimate/सुकपानी स्याले सिंचाई कुलो मर्मत/सुकपानी स्याले सिंचाई कुलो मर्मत.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDCD1D6E-A9E9-48C4-B69C-581C0C925938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20736" windowHeight="11040"/>
   </bookViews>
   <sheets>
     <sheet name="estimate" sheetId="12" r:id="rId1"/>
@@ -42,7 +41,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">estimate!$1:$8</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -75,9 +74,6 @@
     <t>Detail Estimated Sheet</t>
   </si>
   <si>
-    <t>Location:- Shankharapur Municipality 9</t>
-  </si>
-  <si>
     <t>S.N.</t>
   </si>
   <si>
@@ -184,15 +180,18 @@
   </si>
   <si>
     <t>Date:2082/09/03</t>
+  </si>
+  <si>
+    <t>Location:- Shankharapur Municipality 1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -347,9 +346,9 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
@@ -361,7 +360,7 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -385,14 +384,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -411,7 +410,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -426,7 +425,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -443,6 +442,24 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -462,32 +479,14 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Comma 2" xfId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Percent 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Normal 2" xfId="2"/>
+    <cellStyle name="Normal 3" xfId="5"/>
+    <cellStyle name="Percent 2" xfId="4"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -503,7 +502,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -597,7 +596,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -656,11 +655,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Datasheet"/>
       <sheetName val="Abstract"/>
@@ -733,9 +729,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -773,9 +769,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -810,7 +806,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -845,7 +841,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1018,175 +1014,175 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q37"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" style="19" customWidth="1"/>
-    <col min="2" max="2" width="30.85546875" style="19" customWidth="1"/>
-    <col min="3" max="3" width="4.42578125" style="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" style="19" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" style="19" customWidth="1"/>
-    <col min="6" max="6" width="7.28515625" style="19" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="19"/>
+    <col min="1" max="1" width="4.6640625" style="19" customWidth="1"/>
+    <col min="2" max="2" width="30.88671875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="4.44140625" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" style="19" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" style="19" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" style="19" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" style="19"/>
     <col min="8" max="8" width="5" style="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" style="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" style="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.140625" style="19"/>
+    <col min="9" max="9" width="9.5546875" style="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.109375" style="19"/>
     <col min="13" max="16" width="0" style="19" hidden="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="19"/>
+    <col min="17" max="16384" width="9.109375" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-    </row>
-    <row r="2" spans="1:16" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="47" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+    </row>
+    <row r="2" spans="1:16" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="48" t="s">
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
-    </row>
-    <row r="5" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="49" t="s">
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+    </row>
+    <row r="5" spans="1:16" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A5" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
-    </row>
-    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+    </row>
+    <row r="6" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="37"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-    </row>
-    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="39" t="s">
+      <c r="H6" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+    </row>
+    <row r="7" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="45" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="46"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
+    </row>
+    <row r="8" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="40" t="s">
-        <v>41</v>
-      </c>
-      <c r="I7" s="40"/>
-      <c r="J7" s="40"/>
-      <c r="K7" s="40"/>
-    </row>
-    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="B8" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="C8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="D8" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="E8" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="F8" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="G8" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="H8" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="I8" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="J8" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="K8" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="K8" s="15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="141.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:16" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A9" s="16">
         <v>1</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
@@ -1198,10 +1194,10 @@
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="16"/>
       <c r="B10" s="32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10" s="17">
         <v>1</v>
@@ -1237,10 +1233,10 @@
         <v>160.09797821843054</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="4"/>
@@ -1251,7 +1247,7 @@
         <v>6</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I11" s="6">
         <v>866.66</v>
@@ -1262,7 +1258,7 @@
       </c>
       <c r="K11" s="5"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -1275,12 +1271,12 @@
       <c r="J12" s="17"/>
       <c r="K12" s="17"/>
     </row>
-    <row r="13" spans="1:16" ht="254.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="254.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="16">
         <v>2</v>
       </c>
       <c r="B13" s="35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
@@ -1292,10 +1288,10 @@
       <c r="J13" s="17"/>
       <c r="K13" s="17"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="16"/>
       <c r="B14" s="32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" s="17">
         <v>6</v>
@@ -1331,7 +1327,7 @@
         <v>160.09797821843054</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="16"/>
       <c r="B15" s="32"/>
       <c r="C15" s="17">
@@ -1359,7 +1355,7 @@
       <c r="O15" s="36"/>
       <c r="P15" s="36"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="16"/>
       <c r="B16" s="32"/>
       <c r="C16" s="17">
@@ -1387,10 +1383,10 @@
       <c r="O16" s="36"/>
       <c r="P16" s="36"/>
     </row>
-    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="B17" s="34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="4"/>
@@ -1401,7 +1397,7 @@
         <v>23</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I17" s="6">
         <v>6421.62</v>
@@ -1412,10 +1408,10 @@
       </c>
       <c r="K17" s="5"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="16"/>
       <c r="B18" s="32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
@@ -1430,10 +1426,10 @@
       </c>
       <c r="K18" s="17"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="16"/>
       <c r="B19" s="32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
@@ -1448,10 +1444,10 @@
       </c>
       <c r="K19" s="17"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="16"/>
       <c r="B20" s="32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
@@ -1466,10 +1462,10 @@
       </c>
       <c r="K20" s="17"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="16"/>
       <c r="B21" s="32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C21" s="17"/>
       <c r="D21" s="17"/>
@@ -1484,7 +1480,7 @@
       </c>
       <c r="K21" s="17"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="16"/>
       <c r="B22" s="32"/>
       <c r="C22" s="17"/>
@@ -1497,12 +1493,12 @@
       <c r="J22" s="18"/>
       <c r="K22" s="17"/>
     </row>
-    <row r="23" spans="1:17" ht="123" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" ht="123" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="16">
         <v>3</v>
       </c>
       <c r="B23" s="35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
@@ -1514,10 +1510,10 @@
       <c r="J23" s="17"/>
       <c r="K23" s="17"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="16"/>
       <c r="B24" s="32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C24" s="17">
         <v>1</v>
@@ -1538,10 +1534,10 @@
       <c r="J24" s="18"/>
       <c r="K24" s="17"/>
     </row>
-    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="4"/>
@@ -1552,7 +1548,7 @@
         <v>12</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I25" s="6">
         <v>161.58000000000001</v>
@@ -1563,10 +1559,10 @@
       </c>
       <c r="K25" s="5"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="16"/>
       <c r="B26" s="32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C26" s="17"/>
       <c r="D26" s="17"/>
@@ -1581,7 +1577,7 @@
       </c>
       <c r="K26" s="17"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="16"/>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
@@ -1594,12 +1590,12 @@
       <c r="J27" s="17"/>
       <c r="K27" s="17"/>
     </row>
-    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>4</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C28" s="3">
         <v>1</v>
@@ -1612,7 +1608,7 @@
         <v>1</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I28" s="6">
         <v>500</v>
@@ -1623,7 +1619,7 @@
       </c>
       <c r="K28" s="5"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="8"/>
       <c r="C29" s="3"/>
@@ -1636,10 +1632,10 @@
       <c r="J29" s="18"/>
       <c r="K29" s="5"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="21"/>
       <c r="B30" s="22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C30" s="23"/>
       <c r="D30" s="24"/>
@@ -1654,23 +1650,23 @@
       </c>
       <c r="K30" s="25"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="M31" s="20"/>
       <c r="N31" s="20"/>
       <c r="O31" s="20"/>
       <c r="P31" s="20"/>
       <c r="Q31" s="20"/>
     </row>
-    <row r="32" spans="1:17" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="26"/>
       <c r="B32" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="C32" s="37">
+        <v>20</v>
+      </c>
+      <c r="C32" s="43">
         <f>J30</f>
         <v>169416.86951250001</v>
       </c>
-      <c r="D32" s="38"/>
+      <c r="D32" s="44"/>
       <c r="E32" s="9">
         <v>100</v>
       </c>
@@ -1686,79 +1682,72 @@
       <c r="P32" s="19"/>
       <c r="Q32" s="19"/>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="47">
+        <v>150000</v>
+      </c>
+      <c r="D33" s="48"/>
+      <c r="E33" s="9"/>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B34" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C33" s="41">
-        <v>150000</v>
-      </c>
-      <c r="D33" s="42"/>
-      <c r="E33" s="9"/>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B34" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="C34" s="41">
+      <c r="C34" s="47">
         <f>C33-C36-C37</f>
         <v>142500</v>
       </c>
-      <c r="D34" s="42"/>
+      <c r="D34" s="48"/>
       <c r="E34" s="9">
         <f>C34/C32*100</f>
         <v>84.112048823736515</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="C35" s="43">
+        <v>28</v>
+      </c>
+      <c r="C35" s="49">
         <f>C32-C34</f>
         <v>26916.869512500009</v>
       </c>
-      <c r="D35" s="43"/>
+      <c r="D35" s="49"/>
       <c r="E35" s="9">
         <f>100-E34</f>
         <v>15.887951176263485</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="37">
+        <v>24</v>
+      </c>
+      <c r="C36" s="43">
         <f>C33*0.03</f>
         <v>4500</v>
       </c>
-      <c r="D36" s="38"/>
+      <c r="D36" s="44"/>
       <c r="E36" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C37" s="37">
+        <v>25</v>
+      </c>
+      <c r="C37" s="43">
         <f>C33*0.02</f>
         <v>3000</v>
       </c>
-      <c r="D37" s="38"/>
+      <c r="D37" s="44"/>
       <c r="E37" s="9">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="A7:F7"/>
@@ -1767,6 +1756,13 @@
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="C35:D35"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
